--- a/data/single_run/input/casualty_generation_settings/military_force_structure/force_structure_3_brigades_3_battalions_big_r2e_no_r2b.xlsx
+++ b/data/single_run/input/casualty_generation_settings/military_force_structure/force_structure_3_brigades_3_battalions_big_r2e_no_r2b.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,12 +444,47 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>bcas_spawning_points</t>
+          <t>ccp_ids</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>dnbi_spawning_points</t>
+          <t>r1_ids</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>r2b_ids</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>r2e_ids</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>axp_ids</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>neighbor_r1_ids</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>neighbor_r2b_ids</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>neighbor_r2e_ids</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>neighbor_axp_ids</t>
         </is>
       </c>
     </row>
@@ -485,6 +520,33 @@
           <t>r1_br1_bt1_1</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>r2e_br1_1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>axp_br1_1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>r1_br1_bt3_1,r1_br1_bt2_1</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>r2e_br3_1,r2e_br2_1</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>axp_br3_1,axp_br2_1</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -518,6 +580,33 @@
           <t>r1_br1_bt2_1</t>
         </is>
       </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>r2e_br1_1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>axp_br1_1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>r1_br1_bt1_1,r1_br1_bt3_1</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>r2e_br3_1,r2e_br2_1</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>axp_br3_1,axp_br2_1</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -551,6 +640,33 @@
           <t>r1_br1_bt3_1</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>r2e_br1_1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>axp_br1_1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>r1_br1_bt2_1,r1_br1_bt1_1</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>r2e_br3_1,r2e_br2_1</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>axp_br3_1,axp_br2_1</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -584,6 +700,33 @@
           <t>r1_br2_bt1_1</t>
         </is>
       </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>r2e_br2_1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>axp_br2_1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>r1_br2_bt3_1,r1_br2_bt2_1</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>r2e_br1_1,r2e_br3_1</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>axp_br1_1,axp_br3_1</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -617,6 +760,33 @@
           <t>r1_br2_bt2_1</t>
         </is>
       </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>r2e_br2_1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>axp_br2_1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>r1_br2_bt1_1,r1_br2_bt3_1</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>r2e_br1_1,r2e_br3_1</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>axp_br1_1,axp_br3_1</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -650,6 +820,33 @@
           <t>r1_br2_bt3_1</t>
         </is>
       </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>r2e_br2_1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>axp_br2_1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>r1_br2_bt2_1,r1_br2_bt1_1</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>r2e_br1_1,r2e_br3_1</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>axp_br1_1,axp_br3_1</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -683,6 +880,33 @@
           <t>r1_br3_bt1_1</t>
         </is>
       </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>r2e_br3_1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>axp_br3_1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>r1_br3_bt3_1,r1_br3_bt2_1</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>r2e_br2_1,r2e_br1_1</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>axp_br2_1,axp_br1_1</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -716,6 +940,33 @@
           <t>r1_br3_bt2_1</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>r2e_br3_1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>axp_br3_1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>r1_br3_bt1_1,r1_br3_bt3_1</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>r2e_br2_1,r2e_br1_1</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>axp_br2_1,axp_br1_1</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -747,6 +998,33 @@
       <c r="G10" t="inlineStr">
         <is>
           <t>r1_br3_bt3_1</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>r2e_br3_1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>axp_br3_1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>r1_br3_bt2_1,r1_br3_bt1_1</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>r2e_br2_1,r2e_br1_1</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>axp_br2_1,axp_br1_1</t>
         </is>
       </c>
     </row>
